--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,6 +133,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -157,6 +161,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -169,20 +181,12 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>PE</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>成交量</t>
@@ -613,7 +617,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -793,6 +797,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -802,7 +809,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -981,6 +988,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1024,7 +1034,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1204,6 +1214,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1213,7 +1226,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1393,6 +1406,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16470742.053078819</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16842108.331714839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1435,7 +1451,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1615,6 +1631,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1624,7 +1643,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1804,6 +1823,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7109407.2353513949</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7480773.5139874145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1825,11 +1847,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="402019072"/>
-        <c:axId val="402023936"/>
+        <c:axId val="453607808"/>
+        <c:axId val="453617920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="402019072"/>
+        <c:axId val="453607808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1872,14 +1894,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="402023936"/>
+        <c:crossAx val="453617920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="402023936"/>
+        <c:axId val="453617920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1930,7 +1952,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="402019072"/>
+        <c:crossAx val="453607808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2121,7 +2143,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2301,6 +2323,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-2500093.7589145182</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-10715332.987082755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2315,8 +2340,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="624593920"/>
-        <c:axId val="624592384"/>
+        <c:axId val="575500288"/>
+        <c:axId val="574867712"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2341,7 +2366,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2521,6 +2546,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2530,7 +2558,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2710,6 +2738,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2726,11 +2757,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="624543616"/>
-        <c:axId val="624545152"/>
+        <c:axId val="574802560"/>
+        <c:axId val="574866176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="624543616"/>
+        <c:axId val="574802560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2773,14 +2804,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624545152"/>
+        <c:crossAx val="574866176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="624545152"/>
+        <c:axId val="574866176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2831,12 +2862,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624543616"/>
+        <c:crossAx val="574802560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="624592384"/>
+        <c:axId val="574867712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2873,12 +2904,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624593920"/>
+        <c:crossAx val="575500288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="624593920"/>
+        <c:axId val="575500288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2887,7 +2918,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="624592384"/>
+        <c:crossAx val="574867712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3049,7 +3080,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3229,6 +3260,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3243,8 +3277,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="403247488"/>
-        <c:axId val="402060800"/>
+        <c:axId val="453807104"/>
+        <c:axId val="453804800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3269,7 +3303,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3449,6 +3483,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3458,7 +3495,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3638,6 +3675,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3654,11 +3694,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="402048128"/>
-        <c:axId val="402049664"/>
+        <c:axId val="453771264"/>
+        <c:axId val="453772800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="402048128"/>
+        <c:axId val="453771264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3701,14 +3741,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="402049664"/>
+        <c:crossAx val="453772800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="402049664"/>
+        <c:axId val="453772800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3759,12 +3799,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="402048128"/>
+        <c:crossAx val="453771264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="402060800"/>
+        <c:axId val="453804800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3801,12 +3841,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403247488"/>
+        <c:crossAx val="453807104"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="403247488"/>
+        <c:axId val="453807104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3815,7 +3855,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="402060800"/>
+        <c:crossAx val="453804800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3994,7 +4034,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4174,6 +4214,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4183,7 +4226,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4362,6 +4405,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4405,7 +4451,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4585,6 +4631,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4594,7 +4643,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4774,6 +4823,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17697629.703050636</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18094777.250086345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4816,7 +4868,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4996,6 +5048,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5005,7 +5060,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5185,6 +5240,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7689856.1635277644</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8087003.7105634734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5206,11 +5264,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="403298560"/>
-        <c:axId val="403300352"/>
+        <c:axId val="539178880"/>
+        <c:axId val="539180416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="403298560"/>
+        <c:axId val="539178880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5253,14 +5311,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403300352"/>
+        <c:crossAx val="539180416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="403300352"/>
+        <c:axId val="539180416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5311,7 +5369,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403298560"/>
+        <c:crossAx val="539178880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5502,7 +5560,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5682,6 +5740,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-394977.32401696721</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1098753.7286700674</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5696,8 +5757,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="617034112"/>
-        <c:axId val="571240832"/>
+        <c:axId val="552692736"/>
+        <c:axId val="552690816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5722,7 +5783,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5902,6 +5963,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5911,7 +5975,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6091,6 +6155,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6107,11 +6174,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494914176"/>
-        <c:axId val="546480512"/>
+        <c:axId val="552670720"/>
+        <c:axId val="552672640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494914176"/>
+        <c:axId val="552670720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6154,14 +6221,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546480512"/>
+        <c:crossAx val="552672640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546480512"/>
+        <c:axId val="552672640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6212,12 +6279,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494914176"/>
+        <c:crossAx val="552670720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="571240832"/>
+        <c:axId val="552690816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6254,12 +6321,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617034112"/>
+        <c:crossAx val="552692736"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="617034112"/>
+        <c:axId val="552692736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6268,7 +6335,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="571240832"/>
+        <c:crossAx val="552690816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6447,7 +6514,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6627,6 +6694,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6636,7 +6706,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6815,6 +6885,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6858,7 +6931,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7038,6 +7111,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7047,7 +7123,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7227,6 +7303,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17567754.333578344</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17963358.223627001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7269,7 +7348,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7449,6 +7528,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7458,7 +7540,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7638,6 +7720,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7604968.9543284345</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8000572.8443770912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7659,11 +7744,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617065472"/>
-        <c:axId val="617071744"/>
+        <c:axId val="570023296"/>
+        <c:axId val="570025088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617065472"/>
+        <c:axId val="570023296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7706,14 +7791,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617071744"/>
+        <c:crossAx val="570025088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617071744"/>
+        <c:axId val="570025088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7764,7 +7849,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617065472"/>
+        <c:crossAx val="570023296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7955,7 +8040,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8135,6 +8220,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-394977.32401696721</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8149,8 +8237,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="621931904"/>
-        <c:axId val="621930368"/>
+        <c:axId val="573962112"/>
+        <c:axId val="573960192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8175,7 +8263,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8355,6 +8443,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8364,7 +8455,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8544,6 +8635,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8560,11 +8654,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621893888"/>
-        <c:axId val="621928448"/>
+        <c:axId val="573693952"/>
+        <c:axId val="573695488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621893888"/>
+        <c:axId val="573693952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8607,14 +8701,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621928448"/>
+        <c:crossAx val="573695488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621928448"/>
+        <c:axId val="573695488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8665,12 +8759,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621893888"/>
+        <c:crossAx val="573693952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="621930368"/>
+        <c:axId val="573960192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8707,12 +8801,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621931904"/>
+        <c:crossAx val="573962112"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="621931904"/>
+        <c:axId val="573962112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8721,7 +8815,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="621930368"/>
+        <c:crossAx val="573960192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8900,7 +8994,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9080,6 +9174,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9089,7 +9186,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9268,6 +9365,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9311,7 +9411,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9491,6 +9591,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9500,7 +9603,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9680,6 +9783,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>157278204.92011258</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>160901580.29612678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9722,7 +9828,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9902,6 +10008,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9911,7 +10020,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10091,6 +10200,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>69838252.257509872</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>73461627.633524075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10112,11 +10224,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622215168"/>
-        <c:axId val="622217088"/>
+        <c:axId val="574099456"/>
+        <c:axId val="574100992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622215168"/>
+        <c:axId val="574099456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10159,14 +10271,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622217088"/>
+        <c:crossAx val="574100992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="622217088"/>
+        <c:axId val="574100992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10217,7 +10329,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622215168"/>
+        <c:crossAx val="574099456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10408,7 +10520,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10588,6 +10700,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>116883008.32632542</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>105957807.12580833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10602,8 +10717,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="623033728"/>
-        <c:axId val="623032192"/>
+        <c:axId val="574468864"/>
+        <c:axId val="574325504"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10628,7 +10743,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10808,6 +10923,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10817,7 +10935,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10997,6 +11115,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11013,11 +11134,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="622778624"/>
-        <c:axId val="623030272"/>
+        <c:axId val="574305408"/>
+        <c:axId val="574306944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="622778624"/>
+        <c:axId val="574305408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11060,14 +11181,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623030272"/>
+        <c:crossAx val="574306944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623030272"/>
+        <c:axId val="574306944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11118,12 +11239,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="622778624"/>
+        <c:crossAx val="574305408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="623032192"/>
+        <c:axId val="574325504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11160,12 +11281,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623033728"/>
+        <c:crossAx val="574468864"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="623033728"/>
+        <c:axId val="574468864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11174,7 +11295,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="623032192"/>
+        <c:crossAx val="574325504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11353,7 +11474,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11533,6 +11654,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11542,7 +11666,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11721,6 +11845,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11764,7 +11891,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11944,6 +12071,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11953,7 +12083,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12133,6 +12263,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>162688850.00592482</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>166564935.16431901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12175,7 +12308,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12355,6 +12488,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12364,7 +12500,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12544,6 +12680,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>79107853.670304805</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>82983938.828698993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12565,11 +12704,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623904640"/>
-        <c:axId val="623906176"/>
+        <c:axId val="574579840"/>
+        <c:axId val="574581760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623904640"/>
+        <c:axId val="574579840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12612,14 +12751,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623906176"/>
+        <c:crossAx val="574581760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623906176"/>
+        <c:axId val="574581760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12670,7 +12809,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623904640"/>
+        <c:crossAx val="574579840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13384,7 +13523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13515,28 +13654,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -16025,6 +16164,44 @@
       </c>
       <c r="L62" s="14">
         <v>1556201.7813372496</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>11261973.499519134</v>
+      </c>
+      <c r="H63" s="15">
+        <v>14370278.443152532</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J63" s="15">
+        <v>16842108.331714839</v>
+      </c>
+      <c r="K63" s="15">
+        <v>7480773.5139874145</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2471829.8885623058</v>
       </c>
     </row>
   </sheetData>
@@ -16043,7 +16220,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16078,10 +16255,10 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -16114,10 +16291,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -16138,7 +16315,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -16218,28 +16395,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -20137,6 +20314,71 @@
         <v>128.75846332158676</v>
       </c>
       <c r="U62" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-1098753.7286700674</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-861092.24840221775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>11950111.458020555</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15248342.493950574</v>
+      </c>
+      <c r="I63" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J63" s="15">
+        <v>18094777.250086345</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8087003.7105634734</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2846434.7561357729</v>
+      </c>
+      <c r="M63" s="23">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="N63" s="23">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="O63" s="23">
+        <v>1.2480000257492065</v>
+      </c>
+      <c r="P63" s="23">
+        <v>1.0304285770370849</v>
+      </c>
+      <c r="Q63" s="23">
+        <v>0.21757144871212164</v>
+      </c>
+      <c r="R63" s="23">
+        <v>0.10519728409189744</v>
+      </c>
+      <c r="S63" s="9">
+        <v>1.5779592613784615E-3</v>
+      </c>
+      <c r="T63" s="9">
+        <v>137.88153727242442</v>
+      </c>
+      <c r="U63" s="11">
         <v>1.2</v>
       </c>
     </row>
@@ -20156,7 +20398,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20194,7 +20436,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>9</v>
@@ -20230,7 +20472,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -20297,28 +20539,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -23146,6 +23388,50 @@
       </c>
       <c r="N62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>12043831.475181028</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15367929.237992419</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J63" s="15">
+        <v>17963358.223627001</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8000572.8443770912</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2595428.9856345826</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23164,7 +23450,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23199,13 +23485,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -23238,7 +23524,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -23305,28 +23591,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -26154,6 +26440,50 @@
       </c>
       <c r="N62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-13940556.981917825</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-10925201.200517096</v>
+      </c>
+      <c r="G63" s="15">
+        <v>105957807.12580833</v>
+      </c>
+      <c r="H63" s="15">
+        <v>135202164.31771317</v>
+      </c>
+      <c r="I63" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J63" s="15">
+        <v>160901580.29612678</v>
+      </c>
+      <c r="K63" s="15">
+        <v>73461627.633524075</v>
+      </c>
+      <c r="L63" s="14">
+        <v>25699415.978413627</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -26172,7 +26502,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26207,22 +26537,22 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -26252,7 +26582,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -26327,28 +26657,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -29530,6 +29860,56 @@
       </c>
       <c r="P62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="14">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="14">
+        <v>-10715332.987082755</v>
+      </c>
+      <c r="H63" s="15">
+        <v>-8397596.2342296485</v>
+      </c>
+      <c r="I63" s="15">
+        <v>116637335.79108463</v>
+      </c>
+      <c r="J63" s="15">
+        <v>148829243.13904074</v>
+      </c>
+      <c r="K63" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L63" s="15">
+        <v>166564935.16431901</v>
+      </c>
+      <c r="M63" s="15">
+        <v>82983938.828698993</v>
+      </c>
+      <c r="N63" s="14">
+        <v>17735692.025278274</v>
+      </c>
+      <c r="O63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="P63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -169,6 +165,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -178,14 +178,6 @@
   </si>
   <si>
     <t>标志</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -617,7 +609,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -800,6 +792,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -809,7 +804,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -991,6 +986,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1034,7 +1032,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1217,6 +1215,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1226,7 +1227,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1409,6 +1410,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>16842108.331714839</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>14938834.477348203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1451,7 +1455,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1634,6 +1638,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1643,7 +1650,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1826,6 +1833,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>7480773.5139874145</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5577499.6596207786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1847,11 +1857,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="453607808"/>
-        <c:axId val="453617920"/>
+        <c:axId val="411966464"/>
+        <c:axId val="411976448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="453607808"/>
+        <c:axId val="411966464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1894,14 +1904,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453617920"/>
+        <c:crossAx val="411976448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="453617920"/>
+        <c:axId val="411976448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1952,7 +1962,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453607808"/>
+        <c:crossAx val="411966464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2143,7 +2153,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2326,6 +2336,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-10715332.987082755</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-3137492.7659313167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2340,8 +2353,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="575500288"/>
-        <c:axId val="574867712"/>
+        <c:axId val="728700032"/>
+        <c:axId val="728697088"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2366,7 +2379,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2549,6 +2562,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2558,7 +2574,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2741,6 +2757,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2757,11 +2776,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574802560"/>
-        <c:axId val="574866176"/>
+        <c:axId val="728689664"/>
+        <c:axId val="728695552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574802560"/>
+        <c:axId val="728689664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2804,14 +2823,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574866176"/>
+        <c:crossAx val="728695552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574866176"/>
+        <c:axId val="728695552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2862,12 +2881,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574802560"/>
+        <c:crossAx val="728689664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="574867712"/>
+        <c:axId val="728697088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2904,12 +2923,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="575500288"/>
+        <c:crossAx val="728700032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="575500288"/>
+        <c:axId val="728700032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2918,7 +2937,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="574867712"/>
+        <c:crossAx val="728697088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3080,7 +3099,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3263,6 +3282,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3277,8 +3299,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="453807104"/>
-        <c:axId val="453804800"/>
+        <c:axId val="491439616"/>
+        <c:axId val="491438080"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3303,7 +3325,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3486,6 +3508,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3495,7 +3520,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3678,6 +3703,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3694,11 +3722,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="453771264"/>
-        <c:axId val="453772800"/>
+        <c:axId val="491417984"/>
+        <c:axId val="491419904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="453771264"/>
+        <c:axId val="491417984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3741,14 +3769,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453772800"/>
+        <c:crossAx val="491419904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="453772800"/>
+        <c:axId val="491419904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3799,12 +3827,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453771264"/>
+        <c:crossAx val="491417984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="453804800"/>
+        <c:axId val="491438080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3841,12 +3869,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453807104"/>
+        <c:crossAx val="491439616"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="453807104"/>
+        <c:axId val="491439616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3855,7 +3883,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="453804800"/>
+        <c:crossAx val="491438080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4034,7 +4062,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4217,6 +4245,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4226,7 +4257,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4408,6 +4439,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4451,7 +4485,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4634,6 +4668,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4643,7 +4680,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4826,6 +4863,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18094777.250086345</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16075208.060388925</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4868,7 +4908,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5051,6 +5091,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5060,7 +5103,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5243,6 +5286,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8087003.7105634734</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6067434.5208660532</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5264,11 +5310,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="539178880"/>
-        <c:axId val="539180416"/>
+        <c:axId val="564808320"/>
+        <c:axId val="692078464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="539178880"/>
+        <c:axId val="564808320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5311,14 +5357,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539180416"/>
+        <c:crossAx val="692078464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="539180416"/>
+        <c:axId val="692078464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5369,7 +5415,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539178880"/>
+        <c:crossAx val="564808320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5560,7 +5606,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5743,6 +5789,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-1098753.7286700674</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5757,8 +5806,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="552692736"/>
-        <c:axId val="552690816"/>
+        <c:axId val="697677696"/>
+        <c:axId val="697631872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5783,7 +5832,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5966,6 +6015,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5975,7 +6027,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6158,6 +6210,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6174,11 +6229,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="552670720"/>
-        <c:axId val="552672640"/>
+        <c:axId val="693164672"/>
+        <c:axId val="693529984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="552670720"/>
+        <c:axId val="693164672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6221,14 +6276,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="552672640"/>
+        <c:crossAx val="693529984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="552672640"/>
+        <c:axId val="693529984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6279,12 +6334,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="552670720"/>
+        <c:crossAx val="693164672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="552690816"/>
+        <c:axId val="697631872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6321,12 +6376,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="552692736"/>
+        <c:crossAx val="697677696"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="552692736"/>
+        <c:axId val="697677696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6335,7 +6390,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="552690816"/>
+        <c:crossAx val="697631872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6514,7 +6569,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6697,6 +6752,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6706,7 +6764,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6888,6 +6946,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6931,7 +6992,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7114,6 +7175,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7123,7 +7187,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7306,6 +7370,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17963358.223627001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15927950.34825873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7348,7 +7415,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7531,6 +7598,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7540,7 +7610,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7723,6 +7793,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8000572.8443770912</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5965164.9690088201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7744,11 +7817,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="570023296"/>
-        <c:axId val="570025088"/>
+        <c:axId val="721703296"/>
+        <c:axId val="721705984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="570023296"/>
+        <c:axId val="721703296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7791,14 +7864,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="570025088"/>
+        <c:crossAx val="721705984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="570025088"/>
+        <c:axId val="721705984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7849,7 +7922,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="570023296"/>
+        <c:crossAx val="721703296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8040,7 +8113,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8223,6 +8296,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-915628.10722505616</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-314574.39222416701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8237,8 +8313,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="573962112"/>
-        <c:axId val="573960192"/>
+        <c:axId val="726080896"/>
+        <c:axId val="726079360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8263,7 +8339,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8446,6 +8522,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8455,7 +8534,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8638,6 +8717,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8654,11 +8736,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573693952"/>
-        <c:axId val="573695488"/>
+        <c:axId val="721744640"/>
+        <c:axId val="721747328"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573693952"/>
+        <c:axId val="721744640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8701,14 +8783,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573695488"/>
+        <c:crossAx val="721747328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573695488"/>
+        <c:axId val="721747328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8759,12 +8841,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573693952"/>
+        <c:crossAx val="721744640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="573960192"/>
+        <c:axId val="726079360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8801,12 +8883,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573962112"/>
+        <c:crossAx val="726080896"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="573962112"/>
+        <c:axId val="726080896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8815,7 +8897,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="573960192"/>
+        <c:crossAx val="726079360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8994,7 +9076,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9177,6 +9259,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9186,7 +9271,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9368,6 +9453,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9411,7 +9499,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9594,6 +9682,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9603,7 +9694,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9786,6 +9877,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>160901580.29612678</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>142994707.75933877</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9828,7 +9922,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10011,6 +10105,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10020,7 +10117,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10203,6 +10300,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>73461627.633524075</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>55554755.096736059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10224,11 +10324,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574099456"/>
-        <c:axId val="574100992"/>
+        <c:axId val="726516096"/>
+        <c:axId val="726518016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574099456"/>
+        <c:axId val="726516096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10271,14 +10371,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574100992"/>
+        <c:crossAx val="726518016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574100992"/>
+        <c:axId val="726518016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10329,7 +10429,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574099456"/>
+        <c:crossAx val="726516096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10520,7 +10620,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10703,6 +10803,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>105957807.12580833</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>103421867.6557951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10717,8 +10820,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="574468864"/>
-        <c:axId val="574325504"/>
+        <c:axId val="727767680"/>
+        <c:axId val="727765760"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10743,7 +10846,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10926,6 +11029,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10935,7 +11041,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11118,6 +11224,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11134,11 +11243,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574305408"/>
-        <c:axId val="574306944"/>
+        <c:axId val="727020672"/>
+        <c:axId val="727022592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574305408"/>
+        <c:axId val="727020672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11181,14 +11290,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574306944"/>
+        <c:crossAx val="727022592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574306944"/>
+        <c:axId val="727022592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11239,12 +11348,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574305408"/>
+        <c:crossAx val="727020672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="574325504"/>
+        <c:axId val="727765760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11281,12 +11390,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574468864"/>
+        <c:crossAx val="727767680"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="574468864"/>
+        <c:axId val="727767680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11295,7 +11404,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="574325504"/>
+        <c:crossAx val="727765760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11474,7 +11583,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11657,6 +11766,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11666,7 +11778,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11848,6 +11960,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -11891,7 +12006,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12074,6 +12189,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12083,7 +12201,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12266,6 +12384,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>166564935.16431901</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>146853221.96737075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12308,7 +12429,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12491,6 +12612,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12500,7 +12624,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12683,6 +12807,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>82983938.828698993</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>63272225.631750733</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12704,11 +12831,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="574579840"/>
-        <c:axId val="574581760"/>
+        <c:axId val="728216704"/>
+        <c:axId val="728218240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="574579840"/>
+        <c:axId val="728216704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12751,14 +12878,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574581760"/>
+        <c:crossAx val="728218240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="574581760"/>
+        <c:axId val="728218240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12809,7 +12936,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574579840"/>
+        <c:crossAx val="728216704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13523,7 +13650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13654,28 +13781,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -16202,6 +16329,44 @@
       </c>
       <c r="L63" s="14">
         <v>2471829.8885623058</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>10977805.121812543</v>
+      </c>
+      <c r="H64" s="15">
+        <v>12152430.19656173</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J64" s="15">
+        <v>14938834.477348203</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5577499.6596207786</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2786404.2807864728</v>
       </c>
     </row>
   </sheetData>
@@ -16220,7 +16385,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16255,13 +16420,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="25" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -16395,28 +16560,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -20380,6 +20545,71 @@
       </c>
       <c r="U63" s="11">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11665943.080313964</v>
+      </c>
+      <c r="H64" s="15">
+        <v>12914198.912028985</v>
+      </c>
+      <c r="I64" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J64" s="15">
+        <v>16075208.060388925</v>
+      </c>
+      <c r="K64" s="15">
+        <v>6067434.5208660532</v>
+      </c>
+      <c r="L64" s="14">
+        <v>3161009.1483599399</v>
+      </c>
+      <c r="M64" s="23">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="N64" s="23">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="O64" s="23">
+        <v>1.1546666622161865</v>
+      </c>
+      <c r="P64" s="23">
+        <v>1.0564761956532798</v>
+      </c>
+      <c r="Q64" s="23">
+        <v>9.8190466562906753E-2</v>
+      </c>
+      <c r="R64" s="23">
+        <v>8.5721089726402591E-2</v>
+      </c>
+      <c r="S64" s="9">
+        <v>1.2858163458960388E-3</v>
+      </c>
+      <c r="T64" s="9">
+        <v>76.364301073246494</v>
+      </c>
+      <c r="U64" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -20398,7 +20628,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20433,13 +20663,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B1" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -20539,28 +20769,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -23431,6 +23661,50 @@
         <v>66.335527216233743</v>
       </c>
       <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11759663.097474437</v>
+      </c>
+      <c r="H64" s="15">
+        <v>13017946.970399981</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J64" s="15">
+        <v>15927950.34825873</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5965164.9690088201</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2910003.3778587496</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
         <v>1</v>
       </c>
     </row>
@@ -23450,7 +23724,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23488,10 +23762,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -23591,28 +23865,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -26483,6 +26757,50 @@
         <v>66.335527216233743</v>
       </c>
       <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-2807284.9763754238</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-2535939.4700132306</v>
+      </c>
+      <c r="G64" s="15">
+        <v>103421867.6557951</v>
+      </c>
+      <c r="H64" s="15">
+        <v>114488006.80454972</v>
+      </c>
+      <c r="I64" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J64" s="15">
+        <v>142994707.75933877</v>
+      </c>
+      <c r="K64" s="15">
+        <v>55554755.096736059</v>
+      </c>
+      <c r="L64" s="14">
+        <v>28506700.95478905</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
         <v>1</v>
       </c>
     </row>
@@ -26502,7 +26820,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26540,19 +26858,19 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -26657,28 +26975,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -29909,6 +30227,56 @@
         <v>66.335527216233743</v>
       </c>
       <c r="P63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>4485200</v>
+      </c>
+      <c r="F64" s="14">
+        <v>4013151.7473958335</v>
+      </c>
+      <c r="G64" s="14">
+        <v>-3137492.7659313167</v>
+      </c>
+      <c r="H64" s="15">
+        <v>-2834230.1579510788</v>
+      </c>
+      <c r="I64" s="15">
+        <v>113803105.63313356</v>
+      </c>
+      <c r="J64" s="15">
+        <v>125980037.17616116</v>
+      </c>
+      <c r="K64" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L64" s="15">
+        <v>146853221.96737075</v>
+      </c>
+      <c r="M64" s="15">
+        <v>63272225.631750733</v>
+      </c>
+      <c r="N64" s="14">
+        <v>20873184.79120959</v>
+      </c>
+      <c r="O64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="P64" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(CCI)cn.xlsx
@@ -157,16 +157,8 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>深创100ETF</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -175,6 +167,14 @@
   <si>
     <t>最低价</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>标志</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>标志</t>
@@ -609,7 +609,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -795,6 +795,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -804,7 +807,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -989,6 +992,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1032,7 +1038,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1218,6 +1224,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,7 +1236,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1413,6 +1422,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14938834.477348203</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15015678.778184865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1455,7 +1467,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1641,6 +1653,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1650,7 +1665,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1836,6 +1851,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5577499.6596207786</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5654343.9604574405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1857,11 +1875,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="411966464"/>
-        <c:axId val="411976448"/>
+        <c:axId val="159283456"/>
+        <c:axId val="159285632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="411966464"/>
+        <c:axId val="159283456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1904,14 +1922,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="411976448"/>
+        <c:crossAx val="159285632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="411976448"/>
+        <c:axId val="159285632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1962,7 +1980,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="411966464"/>
+        <c:crossAx val="159283456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2153,7 +2171,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2339,6 +2357,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-3137492.7659313167</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-1153306.5826965235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2353,8 +2374,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="728700032"/>
-        <c:axId val="728697088"/>
+        <c:axId val="531284736"/>
+        <c:axId val="531158528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2379,7 +2400,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2565,6 +2586,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2574,7 +2598,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2760,6 +2784,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2776,11 +2803,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="728689664"/>
-        <c:axId val="728695552"/>
+        <c:axId val="531145472"/>
+        <c:axId val="531147008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="728689664"/>
+        <c:axId val="531145472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2823,14 +2850,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728695552"/>
+        <c:crossAx val="531147008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="728695552"/>
+        <c:axId val="531147008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2881,12 +2908,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728689664"/>
+        <c:crossAx val="531145472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="728697088"/>
+        <c:axId val="531158528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2923,12 +2950,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728700032"/>
+        <c:crossAx val="531284736"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="728700032"/>
+        <c:axId val="531284736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2937,7 +2964,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="728697088"/>
+        <c:crossAx val="531158528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3099,7 +3126,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3285,6 +3312,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3299,8 +3329,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="491439616"/>
-        <c:axId val="491438080"/>
+        <c:axId val="159784320"/>
+        <c:axId val="159782400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3325,7 +3355,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3511,6 +3541,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3520,7 +3553,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3706,6 +3739,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3722,11 +3758,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="491417984"/>
-        <c:axId val="491419904"/>
+        <c:axId val="159316224"/>
+        <c:axId val="159397376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="491417984"/>
+        <c:axId val="159316224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3769,14 +3805,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="491419904"/>
+        <c:crossAx val="159397376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="491419904"/>
+        <c:axId val="159397376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3827,12 +3863,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="491417984"/>
+        <c:crossAx val="159316224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="491438080"/>
+        <c:axId val="159782400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3869,12 +3905,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="491439616"/>
+        <c:crossAx val="159784320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="491439616"/>
+        <c:axId val="159784320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3883,7 +3919,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="491438080"/>
+        <c:crossAx val="159782400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4062,7 +4098,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4248,6 +4284,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4257,7 +4296,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4442,6 +4481,9 @@
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10007773.539522871</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10007773.539522871</c:v>
                 </c:pt>
               </c:numCache>
@@ -4485,7 +4527,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4671,6 +4713,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4680,7 +4725,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4866,6 +4911,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16075208.060388925</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16156869.305934794</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4908,7 +4956,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5094,6 +5142,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5103,7 +5154,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5289,6 +5340,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6067434.5208660532</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6149095.7664119229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5310,11 +5364,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="564808320"/>
-        <c:axId val="692078464"/>
+        <c:axId val="490329216"/>
+        <c:axId val="495093632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="564808320"/>
+        <c:axId val="490329216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5357,14 +5411,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692078464"/>
+        <c:crossAx val="495093632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692078464"/>
+        <c:axId val="495093632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5415,7 +5469,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564808320"/>
+        <c:crossAx val="490329216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5606,7 +5660,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5792,6 +5846,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5806,8 +5863,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="697677696"/>
-        <c:axId val="697631872"/>
+        <c:axId val="527565952"/>
+        <c:axId val="523434624"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5832,7 +5889,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6018,6 +6075,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6027,7 +6087,7 @@
               <c:f>'模型四 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6213,6 +6273,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6229,11 +6292,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="693164672"/>
-        <c:axId val="693529984"/>
+        <c:axId val="500861568"/>
+        <c:axId val="523433088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="693164672"/>
+        <c:axId val="500861568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6276,14 +6339,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693529984"/>
+        <c:crossAx val="523433088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="693529984"/>
+        <c:axId val="523433088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6334,12 +6397,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693164672"/>
+        <c:crossAx val="500861568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="697631872"/>
+        <c:axId val="523434624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6376,12 +6439,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697677696"/>
+        <c:crossAx val="527565952"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="697677696"/>
+        <c:axId val="527565952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6390,7 +6453,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="697631872"/>
+        <c:crossAx val="523434624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6569,7 +6632,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6755,6 +6818,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6764,7 +6830,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6949,6 +7015,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -6992,7 +7061,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7178,6 +7247,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7187,7 +7259,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7373,6 +7445,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15927950.34825873</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16010267.631064614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7415,7 +7490,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7601,6 +7676,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7610,7 +7688,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7796,6 +7874,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5965164.9690088201</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047482.2518147044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7817,11 +7898,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="721703296"/>
-        <c:axId val="721705984"/>
+        <c:axId val="527621504"/>
+        <c:axId val="527623296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="721703296"/>
+        <c:axId val="527621504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7864,14 +7945,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721705984"/>
+        <c:crossAx val="527623296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="721705984"/>
+        <c:axId val="527623296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7922,7 +8003,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721703296"/>
+        <c:crossAx val="527621504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8113,7 +8194,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8299,6 +8380,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8313,8 +8397,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="726080896"/>
-        <c:axId val="726079360"/>
+        <c:axId val="527743616"/>
+        <c:axId val="527703424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8339,7 +8423,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8525,6 +8609,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8534,7 +8621,7 @@
               <c:f>'模型四 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8720,6 +8807,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8736,11 +8826,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="721744640"/>
-        <c:axId val="721747328"/>
+        <c:axId val="527657216"/>
+        <c:axId val="527700352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="721744640"/>
+        <c:axId val="527657216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8783,14 +8873,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721747328"/>
+        <c:crossAx val="527700352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="721747328"/>
+        <c:axId val="527700352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8841,12 +8931,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721744640"/>
+        <c:crossAx val="527657216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="726079360"/>
+        <c:axId val="527703424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8883,12 +8973,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="726080896"/>
+        <c:crossAx val="527743616"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="726080896"/>
+        <c:axId val="527743616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8897,7 +8987,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="726079360"/>
+        <c:crossAx val="527703424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9076,7 +9166,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9262,6 +9352,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9271,7 +9364,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9456,6 +9549,9 @@
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>87439952.662602708</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>87439952.662602708</c:v>
                 </c:pt>
               </c:numCache>
@@ -9499,7 +9595,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9685,6 +9781,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9694,7 +9793,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9880,6 +9979,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>142994707.75933877</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>143718657.6767444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9922,7 +10024,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10108,6 +10210,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10117,7 +10222,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10303,6 +10408,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>55554755.096736059</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>56278705.014141694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10324,11 +10432,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="726516096"/>
-        <c:axId val="726518016"/>
+        <c:axId val="527830400"/>
+        <c:axId val="527877632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="726516096"/>
+        <c:axId val="527830400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10371,14 +10479,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="726518016"/>
+        <c:crossAx val="527877632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="726518016"/>
+        <c:axId val="527877632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10429,7 +10537,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="726516096"/>
+        <c:crossAx val="527830400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10620,7 +10728,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10806,6 +10914,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>103421867.6557951</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>100966483.27033739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10820,8 +10931,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="727767680"/>
-        <c:axId val="727765760"/>
+        <c:axId val="530307328"/>
+        <c:axId val="530305792"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10846,7 +10957,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11032,6 +11143,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11041,7 +11155,7 @@
               <c:f>'模型四 (3)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11227,6 +11341,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11243,11 +11360,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="727020672"/>
-        <c:axId val="727022592"/>
+        <c:axId val="530162432"/>
+        <c:axId val="530163968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="727020672"/>
+        <c:axId val="530162432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11290,14 +11407,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="727022592"/>
+        <c:crossAx val="530163968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="727022592"/>
+        <c:axId val="530163968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11348,12 +11465,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="727020672"/>
+        <c:crossAx val="530162432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="727765760"/>
+        <c:axId val="530305792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11390,12 +11507,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="727767680"/>
+        <c:crossAx val="530307328"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="727767680"/>
+        <c:axId val="530307328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11404,7 +11521,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="727765760"/>
+        <c:crossAx val="530305792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11583,7 +11700,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11769,6 +11886,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11778,7 +11898,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11963,6 +12083,9 @@
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>83580996.335620016</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>83580996.335620016</c:v>
                 </c:pt>
               </c:numCache>
@@ -12006,7 +12129,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12192,6 +12315,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12201,7 +12327,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12387,6 +12513,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>146853221.96737075</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>147649840.2338075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12429,7 +12558,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12615,6 +12744,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12624,7 +12756,7 @@
               <c:f>'模型四 (3)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12810,6 +12942,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>63272225.631750733</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>64068843.898187488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12831,11 +12966,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="728216704"/>
-        <c:axId val="728218240"/>
+        <c:axId val="530932864"/>
+        <c:axId val="530934784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="728216704"/>
+        <c:axId val="530932864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12878,14 +13013,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728218240"/>
+        <c:crossAx val="530934784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="728218240"/>
+        <c:axId val="530934784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12936,7 +13071,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728216704"/>
+        <c:crossAx val="530932864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13650,7 +13785,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16369,6 +16504,44 @@
         <v>2786404.2807864728</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>10700270.628994567</v>
+      </c>
+      <c r="H65" s="15">
+        <v>11920101.082721591</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J65" s="15">
+        <v>15015678.778184865</v>
+      </c>
+      <c r="K65" s="15">
+        <v>5654343.9604574405</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3095577.6954632737</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -16385,7 +16558,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16420,13 +16593,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>26</v>
-      </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -16456,10 +16629,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -16480,7 +16653,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -16560,7 +16733,7 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="W3" s="16" t="s">
         <v>19</v>
@@ -20609,6 +20782,71 @@
         <v>76.364301073246494</v>
       </c>
       <c r="U64" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11388408.587495988</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12686686.742898053</v>
+      </c>
+      <c r="I65" s="15">
+        <v>10007773.539522871</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16156869.305934794</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6149095.7664119229</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3470182.5630367408</v>
+      </c>
+      <c r="M65" s="23">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="N65" s="23">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="O65" s="23">
+        <v>1.1276666720708211</v>
+      </c>
+      <c r="P65" s="23">
+        <v>1.0799047677289875</v>
+      </c>
+      <c r="Q65" s="23">
+        <v>4.7761904341833583E-2</v>
+      </c>
+      <c r="R65" s="23">
+        <v>7.0020411087542242E-2</v>
+      </c>
+      <c r="S65" s="9">
+        <v>1.0503061663131336E-3</v>
+      </c>
+      <c r="T65" s="9">
+        <v>45.47426824074654</v>
+      </c>
+      <c r="U65" s="11">
         <v>1</v>
       </c>
     </row>
@@ -20628,7 +20866,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20663,13 +20901,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>26</v>
-      </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -20702,7 +20940,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -20769,7 +21007,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="16" t="s">
         <v>19</v>
@@ -23705,6 +23943,50 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11482128.604656462</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12791090.838529063</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16010267.631064614</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6047482.2518147044</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3219176.7925355504</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
         <v>1</v>
       </c>
     </row>
@@ -23724,7 +24006,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23759,13 +24041,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -23865,7 +24147,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="16" t="s">
         <v>19</v>
@@ -26801,6 +27083,50 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-2735298.1140760505</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-2455384.385457715</v>
+      </c>
+      <c r="G65" s="15">
+        <v>100966483.27033739</v>
+      </c>
+      <c r="H65" s="15">
+        <v>112476658.60787931</v>
+      </c>
+      <c r="I65" s="15">
+        <v>87439952.662602708</v>
+      </c>
+      <c r="J65" s="15">
+        <v>143718657.6767444</v>
+      </c>
+      <c r="K65" s="15">
+        <v>56278705.014141694</v>
+      </c>
+      <c r="L65" s="14">
+        <v>31241999.068865102</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
         <v>1</v>
       </c>
     </row>
@@ -26820,7 +27146,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26858,10 +27184,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -26900,7 +27226,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -26975,7 +27301,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>19</v>
@@ -30277,6 +30603,56 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="P64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="14">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="14">
+        <v>-1153306.5826965235</v>
+      </c>
+      <c r="H65" s="15">
+        <v>-1035284.2201096574</v>
+      </c>
+      <c r="I65" s="15">
+        <v>112767821.4130239</v>
+      </c>
+      <c r="J65" s="15">
+        <v>125623348.8599014</v>
+      </c>
+      <c r="K65" s="15">
+        <v>83580996.335620016</v>
+      </c>
+      <c r="L65" s="15">
+        <v>147649840.2338075</v>
+      </c>
+      <c r="M65" s="15">
+        <v>64068843.898187488</v>
+      </c>
+      <c r="N65" s="14">
+        <v>22026491.373906113</v>
+      </c>
+      <c r="O65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="P65" s="9">
         <v>1</v>
       </c>
     </row>
